--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1726,8 +1726,16 @@
           <t>18:45 - 19:00</t>
         </is>
       </c>
-      <c r="B46" s="49" t="n"/>
-      <c r="C46" s="50" t="n"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Yahya ÖZTÜRK</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
@@ -1776,13 +1784,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A27:C27"/>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehme\OneDrive\Desktop\Çalıştay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696E73AA-0EF9-4EE9-B02E-852B49757FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63150D9-759F-487F-BF3F-4113BA8D24E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6080" yWindow="1400" windowWidth="32710" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5640" yWindow="1910" windowWidth="32710" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
   <si>
     <t>"Erzincan Jeolojik ve Kültürel Miras" Çalıştayı</t>
   </si>
@@ -106,9 +106,6 @@
   </si>
   <si>
     <t>14:30 - 14:45</t>
-  </si>
-  <si>
-    <t>KAF Zonu ve Ötelenmiş Vadiler</t>
   </si>
   <si>
     <t>Mehmet Akif TAŞ</t>
@@ -859,11 +856,9 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -898,14 +893,16 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1253,18 +1250,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
     </row>
     <row r="3" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
@@ -1272,18 +1269,18 @@
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
     </row>
     <row r="5" spans="1:3" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="6" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -1319,11 +1316,11 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="42"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
@@ -1359,11 +1356,11 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
     </row>
     <row r="14" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
@@ -1371,18 +1368,18 @@
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
     </row>
     <row r="16" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
     </row>
     <row r="17" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
@@ -1432,41 +1429,39 @@
       <c r="A21" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="15"/>
+      <c r="C21" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="10" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="45" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="47"/>
     </row>
     <row r="25" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
@@ -1474,18 +1469,18 @@
       <c r="C25" s="1"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
+      <c r="A26" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
@@ -1500,40 +1495,40 @@
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" s="51"/>
       <c r="C32" s="52"/>
@@ -1544,18 +1539,18 @@
       <c r="C33" s="1"/>
     </row>
     <row r="34" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
+      <c r="A34" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
@@ -1570,68 +1565,68 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B40" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>49</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -1639,7 +1634,7 @@
       <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C44" s="49"/>
+      <c r="C44" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="14">

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1,303 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehme\OneDrive\Desktop\Çalıştay\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63150D9-759F-487F-BF3F-4113BA8D24E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="1910" windowWidth="32710" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5640" yWindow="1910" windowWidth="32710" windowHeight="18040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
-  <si>
-    <t>"Erzincan Jeolojik ve Kültürel Miras" Çalıştayı</t>
-  </si>
-  <si>
-    <t>📅  18 Haziran (Perşembe) 2026</t>
-  </si>
-  <si>
-    <t>OTURUM 1 — ERZİNCAN-OTLUKBELİ OTURUMU</t>
-  </si>
-  <si>
-    <t>Oturum Yürütücüleri:</t>
-  </si>
-  <si>
-    <t>SAAT</t>
-  </si>
-  <si>
-    <t>BİLDİRİ BAŞLIĞI</t>
-  </si>
-  <si>
-    <t>SUNUM YAPAN</t>
-  </si>
-  <si>
-    <t>09:30 - 10:00</t>
-  </si>
-  <si>
-    <t>Başlık</t>
-  </si>
-  <si>
-    <t>Nizamettin KAZANCI</t>
-  </si>
-  <si>
-    <t>10:00 - 10:30</t>
-  </si>
-  <si>
-    <t>Enrico CAPEZZUOLİ</t>
-  </si>
-  <si>
-    <t>10:30 - 10:45  ☕ Çay / Kahve Arası</t>
-  </si>
-  <si>
-    <t>10:45 - 11:00</t>
-  </si>
-  <si>
-    <t>Yakup ÇELİK</t>
-  </si>
-  <si>
-    <t>11:00 - 11:15</t>
-  </si>
-  <si>
-    <t>Yıldırım GÜNGÖR</t>
-  </si>
-  <si>
-    <t>11:15 - 11:30</t>
-  </si>
-  <si>
-    <t>Raif KANDEMİR</t>
-  </si>
-  <si>
-    <t>12:30 - 13:30  🍽️ Öğle Yemeği</t>
-  </si>
-  <si>
-    <t>OTURUM 2 — ERZİNCAN-ÇAĞLAYAN OTURUMU</t>
-  </si>
-  <si>
-    <t>13:30 - 14:00</t>
-  </si>
-  <si>
-    <t>Ezher TAGLİASACCHİ</t>
-  </si>
-  <si>
-    <t>14:00 - 14:15</t>
-  </si>
-  <si>
-    <t>MTA Ekibi-1 (Ali ERGEN)</t>
-  </si>
-  <si>
-    <t>14:15 - 14:30</t>
-  </si>
-  <si>
-    <t>İbrahim KOPAR</t>
-  </si>
-  <si>
-    <t>14:30 - 14:45</t>
-  </si>
-  <si>
-    <t>Mehmet Akif TAŞ</t>
-  </si>
-  <si>
-    <t>14:45 - 15:00</t>
-  </si>
-  <si>
-    <t>Samet ALTINBİLEK</t>
-  </si>
-  <si>
-    <t>15:00 - 15:15</t>
-  </si>
-  <si>
-    <t>Volkan DEDE / Kuddusi ZORLU</t>
-  </si>
-  <si>
-    <t>15:15 - 15:30  ☕ Çay / Kahve Arası</t>
-  </si>
-  <si>
-    <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
-  </si>
-  <si>
-    <t>15:30 - 15:45</t>
-  </si>
-  <si>
-    <t>Kenan İNAN</t>
-  </si>
-  <si>
-    <t>15:45 - 16:00</t>
-  </si>
-  <si>
-    <t>16:00 - 16:15</t>
-  </si>
-  <si>
-    <t>Erdal AKPINAR</t>
-  </si>
-  <si>
-    <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
-  </si>
-  <si>
-    <t>16:45 - 17:00</t>
-  </si>
-  <si>
-    <t>Ali DEMİRSOY</t>
-  </si>
-  <si>
-    <t>17:00 - 17:15</t>
-  </si>
-  <si>
-    <t>Eşref ATABEY</t>
-  </si>
-  <si>
-    <t>17:15 - 17:30</t>
-  </si>
-  <si>
-    <t>Gülpınar AKBULUT</t>
-  </si>
-  <si>
-    <t>17:45 - 18:00</t>
-  </si>
-  <si>
-    <t>Volkanik Koniler</t>
-  </si>
-  <si>
-    <t>Fatma TÜKEL</t>
-  </si>
-  <si>
-    <t>18:00 - 18:15</t>
-  </si>
-  <si>
-    <t>M. Feridun ÇELİKMEN (KEMAV Başkanı)</t>
-  </si>
-  <si>
-    <t>Pınar POLAT</t>
-  </si>
-  <si>
-    <t>Vedat Güngör/Mustafa BAYAM (Erzincan Müze Müd.)</t>
-  </si>
-  <si>
-    <t>16:15 - 16:30  ☕ Çay / Kahve Arası</t>
-  </si>
-  <si>
-    <t>17:30 - 17:45</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="11">
     <font>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1B3A5C"/>
       <sz val="16"/>
-      <color rgb="FF1B3A5C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF4A2D7A"/>
       <sz val="10"/>
-      <color rgb="FF4A2D7A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1B3A5C"/>
       <sz val="10"/>
-      <color rgb="FF1B3A5C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <color rgb="FF333333"/>
       <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF333333"/>
       <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF2980B9"/>
       <sz val="10"/>
-      <color rgb="FF2980B9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF8E6E3C"/>
       <sz val="10"/>
-      <color rgb="FF8E6E3C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="162"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1A6B3C"/>
       <sz val="10"/>
-      <color rgb="FF1A6B3C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="17">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -393,7 +215,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -763,170 +585,245 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="54">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1215,462 +1112,578 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{05F25E42-1BED-4DEC-8B7D-AC8240DA4B05}">
-  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;0de5d414-b6a3-44c8-b7a3-58384e2a4c05&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.90625" customWidth="1"/>
-    <col min="2" max="2" width="50.90625" customWidth="1"/>
-    <col min="3" max="3" width="40.81640625" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" customWidth="1"/>
-    <col min="11" max="11" width="48.36328125" customWidth="1"/>
+    <col width="20.90625" customWidth="1" style="34" min="1" max="1"/>
+    <col width="50.90625" customWidth="1" style="34" min="2" max="2"/>
+    <col width="40.81640625" customWidth="1" style="34" min="3" max="3"/>
+    <col width="10.81640625" customWidth="1" style="34" min="10" max="10"/>
+    <col width="48.36328125" customWidth="1" style="34" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-    </row>
-    <row r="3" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-    </row>
-    <row r="5" spans="1:3" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-    </row>
-    <row r="6" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-    </row>
-    <row r="14" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-    </row>
-    <row r="16" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-    </row>
-    <row r="17" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="47"/>
-    </row>
-    <row r="25" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-    </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-    </row>
-    <row r="33" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C44" s="30"/>
+    <row r="1" ht="30" customHeight="1" s="34">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>"Erzincan Jeolojik ve Kültürel Miras" Çalıştayı</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" s="34">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>📅  18 Haziran (Perşembe) 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1" s="34">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="15.5" customHeight="1" s="34">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>OTURUM 1 — ERZİNCAN-OTLUKBELİ OTURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24.5" customHeight="1" s="34">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.5" customHeight="1" s="34">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>09:30 - 10:00</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>UNESCO Jeoparkları; Barış Çağrılarından Doğa Korumaya Geçiş</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Nizamettin KAZANCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>10:00 - 10:30</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Traverten ve Kalkerli Tufa: Jeolojik ve Kültürel Miras Açısından “Anahtar Unsurlar”</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Enrico CAPEZZUOLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20.5" customHeight="1" s="34">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>10:30 - 10:45  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>10:45 - 11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Yakup ÇELİK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>11:00 - 11:15</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Yıldırım GÜNGÖR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>11:15 - 11:30</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Jeoçeşitlilik ve Çevresel Tehditler</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Raif KANDEMİR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>12:30 - 13:30  🍽️ Öğle Yemeği</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1" s="34">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="34">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>OTURUM 2 — ERZİNCAN-ÇAĞLAYAN OTURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1" s="34">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" s="34">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" s="34">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>13:30 - 14:00</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Akarsu Sistemlerinin Doğal Arşivi: Gürlevik Şelalesi ve Jeomiras Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Ezher TAGLİASACCHİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" s="34">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>14:00 - 14:15</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Erzincan'ın Jeolojik Miras Alanlarına İlişkin Yeni Örnekler</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>MTA Ekibi-1 (Ali ERGEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>14:15 - 14:30</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>İbrahim KOPAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>14:30 - 14:45</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Mehmet Akif TAŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>14:45 - 15:00</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Samet ALTINBİLEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>15:00 - 15:15</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Volkan DEDE / Kuddusi ZORLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" s="34">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>15:15 - 15:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1" s="34">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="1" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="34">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="34">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="34">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="34">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>15:30 - 15:45</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Kenan İNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.5" customHeight="1" s="34">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>15:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Erdal AKPINAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>16:00 - 16:15</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Vedat Güngör/Mustafa BAYAM (Erzincan Müze Müd.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="34">
+      <c r="A32" s="53" t="inlineStr">
+        <is>
+          <t>16:15 - 16:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1" s="34">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="1" t="n"/>
+    </row>
+    <row r="34" ht="15.5" customHeight="1" s="34">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>16:45 - 17:00</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Ali DEMİRSOY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>17:00 - 17:15</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Eşref ATABEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>17:15 - 17:30</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Gülpınar AKBULUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>17:30 - 17:45</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa: Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>Fatma TÜKEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>17:45 - 18:00</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>M. Feridun ÇELİKMEN (KEMAV Başkanı)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>18:00 - 18:15</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Pınar POLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="30" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A32:C32"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5640" yWindow="1910" windowWidth="32710" windowHeight="18040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -215,7 +215,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -224,10 +224,51 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
@@ -236,13 +277,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
@@ -251,148 +292,59 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
       <right/>
       <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FFD0D0D0"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,26 +515,6 @@
       <bottom style="thin">
         <color rgb="FF999999"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -602,106 +534,104 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -711,11 +641,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -728,11 +656,9 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -740,15 +666,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,50 +1035,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="20.90625" customWidth="1" style="34" min="1" max="1"/>
-    <col width="50.90625" customWidth="1" style="34" min="2" max="2"/>
-    <col width="40.81640625" customWidth="1" style="34" min="3" max="3"/>
-    <col width="10.81640625" customWidth="1" style="34" min="10" max="10"/>
-    <col width="48.36328125" customWidth="1" style="34" min="11" max="11"/>
+    <col width="56.453125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="104" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="40.81640625" customWidth="1" min="3" max="3"/>
+    <col width="10.81640625" customWidth="1" min="10" max="10"/>
+    <col width="48.36328125" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="34">
-      <c r="A1" s="35" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>"Erzincan Jeolojik ve Kültürel Miras" Çalıştayı</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1" s="34">
-      <c r="A2" s="37" t="inlineStr">
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>📅  18 Haziran (Perşembe) 2026</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1" s="34">
+    <row r="3" ht="8" customHeight="1">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
     </row>
-    <row r="4" ht="15.5" customHeight="1" s="34">
-      <c r="A4" s="43" t="inlineStr">
+    <row r="4" ht="15.5" customHeight="1">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>OTURUM 1 — ERZİNCAN-OTLUKBELİ OTURUMU</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24.5" customHeight="1" s="34">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5" ht="24.5" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15.5" customHeight="1" s="34">
+    <row r="6" ht="15.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SAAT</t>
@@ -1212,8 +1129,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20.5" customHeight="1" s="34">
-      <c r="A9" s="38" t="inlineStr">
+    <row r="9" ht="20.5" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>10:30 - 10:45  ☕ Çay / Kahve Arası</t>
         </is>
@@ -1277,26 +1194,26 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="8" customHeight="1" s="34">
+    <row r="14" ht="8" customHeight="1">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="1" t="n"/>
     </row>
-    <row r="15" ht="21" customHeight="1" s="34">
-      <c r="A15" s="49" t="inlineStr">
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>OTURUM 2 — ERZİNCAN-ÇAĞLAYAN OTURUMU</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21" customHeight="1" s="34">
-      <c r="A16" s="48" t="inlineStr">
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1" s="34">
+    <row r="17" ht="19" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
           <t>SAAT</t>
@@ -1313,7 +1230,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1" s="34">
+    <row r="18" ht="19" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>13:30 - 14:00</t>
@@ -1330,7 +1247,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1" s="34">
+    <row r="19" ht="19" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
           <t>14:00 - 14:15</t>
@@ -1343,7 +1260,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>MTA Ekibi-1 (Ali ERGEN)</t>
+          <t>Ali ERGEN</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1272,12 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>Başlık</t>
+          <t>Polat Gölü'nün Jeolojik-Jeomorfolojik Önemi ve Jeomiras Potansiyeli</t>
         </is>
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>İbrahim KOPAR</t>
+          <t>Mehmet Akif TAŞ</t>
         </is>
       </c>
     </row>
@@ -1370,292 +1287,262 @@
           <t>14:30 - 14:45</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n"/>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Mehmet Akif TAŞ</t>
+          <t>Volkan DEDE / Kuddusi ZORLU</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>14:45 - 15:00</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>15:15 - 15:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1">
+      <c r="A25" s="37" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>15:30 - 15:45</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Samet ALTINBİLEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>15:00 - 15:15</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Kenan İNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>15:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Volkan DEDE / Kuddusi ZORLU</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1" s="34">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t>15:15 - 15:30  ☕ Çay / Kahve Arası</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="8" customHeight="1" s="34">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="1" t="n"/>
-      <c r="C25" s="1" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" s="34">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="34">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Erdal AKPINAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>16:00 - 16:15</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Başlık</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Vedat Güngör/Mustafa BAYAM (Erzincan Müze Müd.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>16:15 - 16:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="1" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1" s="34">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="34" ht="15.5" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>SAAT</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>BİLDİRİ BAŞLIĞI</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>SUNUM YAPAN</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" s="34">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>15:30 - 15:45</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>16:45 - 17:00</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Kenan İNAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17.5" customHeight="1" s="34">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>15:45 - 16:00</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Erdal AKPINAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>16:00 - 16:15</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Vedat Güngör/Mustafa BAYAM (Erzincan Müze Müd.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1" s="34">
-      <c r="A32" s="53" t="inlineStr">
-        <is>
-          <t>16:15 - 16:30  ☕ Çay / Kahve Arası</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="8" customHeight="1" s="34">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="1" t="n"/>
-      <c r="C33" s="1" t="n"/>
-    </row>
-    <row r="34" ht="15.5" customHeight="1" s="34">
-      <c r="A34" s="42" t="inlineStr">
-        <is>
-          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="33" t="inlineStr">
-        <is>
-          <t>Oturum Yürütücüleri:</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Ali DEMİRSOY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SAAT</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>BİLDİRİ BAŞLIĞI</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>SUNUM YAPAN</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>17:00 - 17:15</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Eşref ATABEY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>16:45 - 17:00</t>
+          <t>17:15 - 17:30</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
+          <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa: Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Fatma TÜKEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>17:30 - 17:45</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Ali DEMİRSOY</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>17:00 - 17:15</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Eşref ATABEY</t>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>M. Feridun ÇELİKMEN (KEMAV Başkanı)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>17:15 - 17:30</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>17:45 - 18:00</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Gülpınar AKBULUT</t>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Pınar POLAT</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>17:30 - 17:45</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa: Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>Fatma TÜKEL</t>
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>18:00 - 18:15</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Mutlu SEVEN / Yahya ÖZTÜRK</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>17:45 - 18:00</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>M. Feridun ÇELİKMEN (KEMAV Başkanı)</t>
-        </is>
-      </c>
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>18:00 - 18:15</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Pınar POLAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="n"/>
-    </row>
-    <row r="44">
-      <c r="C44" s="30" t="n"/>
+      <c r="C42" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Başlık</t>
+          <t>Otlukbeli Travertenlerinin Jeolojik-Kültürel Mirası ve Erzincan-Otlukbeli Jeopark Potansiyeli</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Yakup ÇELİK</t>
+          <t>Yakup ÇELİK / Ezher TAGLİASACCHİ / Pınar POLAT / Mehmet Akif TAŞ</t>
         </is>
       </c>
     </row>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Traverten ve Kalkerli Tufa: Jeolojik ve Kültürel Miras Açısından “Anahtar Unsurlar”</t>
+          <t>Travertine and Calcareous Tufa: “Master Keys” in Geological and Cultural Heritage</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Yakup ÇELİK / Ezher TAGLİASACCHİ / Pınar POLAT / Mehmet Akif TAŞ</t>
+          <t>Yakup ÇELİK / Ezher TAGLIASACCHI / Pınar POLAT / Mehmet Akif TAŞ</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Ezher TAGLİASACCHİ</t>
+          <t>Ezher TAGLIASACCHI</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Volkan DEDE / Kuddusi ZORLU</t>
+          <t>Volkan DEDE / Kuttusi ZORLU</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Fatma TÜKEL</t>
+          <t>Fatma Şişman TÜKEL / Yakup ÇELİK / Ali ERGEN</t>
         </is>
       </c>
     </row>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Başlık</t>
+          <t>Jeolojik ve Morfolojik Faktörlerin Erzincan'ın Kültürel Mirasına Katkısı</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Başlık</t>
+          <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>Mehmet Akif TAŞ</t>
+          <t>Mehmet Akif TAŞ / Pınar POLAT / Yakup ÇELİK / Ezher TAGLİASACCHİ</t>
         </is>
       </c>
     </row>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1035,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col width="56.453125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1282,267 +1282,250 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>14:30 - 14:45</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>15:15 - 15:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>15:30 - 15:45</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Coğrafya ve Tarih: 1473 Otlukbeli Savaşının Yerinin Tespiti ve Yol Güzergahları</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Kenan İNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>15:45 - 16:00</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Jeolojik ve Morfolojik Faktörlerin Erzincan'ın Kültürel Mirasına Katkısı</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Erdal AKPINAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>16:00 - 16:15</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Volkan DEDE / Kuttusi ZORLU</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="41" t="inlineStr">
-        <is>
-          <t>15:15 - 15:30  ☕ Çay / Kahve Arası</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="n"/>
-      <c r="C23" s="1" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="40" t="inlineStr">
-        <is>
-          <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="8" customHeight="1">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Vedat Güngör/Mustafa BAYAM (Erzincan Müze Müd.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>16:15 - 16:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="1" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>SAAT</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>BİLDİRİ BAŞLIĞI</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>SUNUM YAPAN</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>15:30 - 15:45</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+    <row r="34" ht="15.5" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>16:45 - 17:00</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Ali DEMİRSOY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>17:00 - 17:15</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Eşref ATABEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>17:15 - 17:30</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa: Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Fatma Şişman TÜKEL / Yakup ÇELİK / Ali ERGEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>17:30 - 17:45</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Kenan İNAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>15:45 - 16:00</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Jeolojik ve Morfolojik Faktörlerin Erzincan'ın Kültürel Mirasına Katkısı</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Erdal AKPINAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>16:00 - 16:15</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>M. Feridun ÇELİKMEN (KEMAV Başkanı)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>17:45 - 18:00</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Vedat Güngör/Mustafa BAYAM (Erzincan Müze Müd.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17.5" customHeight="1">
-      <c r="A30" s="44" t="inlineStr">
-        <is>
-          <t>16:15 - 16:30  ☕ Çay / Kahve Arası</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="1" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="8" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>Oturum Yürütücüleri:</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15.5" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SAAT</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>BİLDİRİ BAŞLIĞI</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>SUNUM YAPAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>16:45 - 17:00</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Ali DEMİRSOY</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>17:00 - 17:15</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Eşref ATABEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>17:15 - 17:30</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa: Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Fatma Şişman TÜKEL / Yakup ÇELİK / Ali ERGEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>17:30 - 17:45</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>M. Feridun ÇELİKMEN (KEMAV Başkanı)</t>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Pınar POLAT</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>17:45 - 18:00</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>Pınar POLAT</t>
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>18:00 - 18:15</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Mutlu SEVEN / Yahya ÖZTÜRK</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>18:00 - 18:15</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Mutlu SEVEN / Yahya ÖZTÜRK</t>
-        </is>
-      </c>
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="n"/>
-    </row>
-    <row r="42">
-      <c r="C42" s="30" t="n"/>
+      <c r="C41" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Başlık</t>
+          <t>Jeolojik Miras Envanter Çalışması Aşamaları</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>Mehmet Akif TAŞ / Pınar POLAT / Yakup ÇELİK / Ezher TAGLİASACCHİ</t>
+          <t>Mehmet Akif TAŞ / Pınar POLAT / Yakup ÇELİK / Ezher TAGLIASACCHI</t>
         </is>
       </c>
     </row>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Enrico CAPEZZUOLİ</t>
+          <t>Enrico CAPEZZUOLI</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Ezher TAGLIASACCHI</t>
+          <t>Ezher TAGLIASACCHI / Yakup ÇELİK</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Ali ERGEN</t>
+          <t>Ali ERGEN / Alper BOZKURT / Ayhan ILGAR / Ercan TUNCAY / Tolga ESİRTGEN / Emine ÖZKAN / Mehmet Akif TAŞ</t>
         </is>
       </c>
     </row>
@@ -1371,14 +1371,14 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Vedat Güngör/Mustafa BAYAM (Erzincan Müze Müd.)</t>
+          <t>Vedat GÜNGÖR / Mustafa BAYAM (Erzincan Müze Müd.)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>16:15 - 16:30  ☕ Çay / Kahve Arası</t>
+          <t>16:15 - 16:45  ☕ Çay / Kahve Arası</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
+          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli Açısından Değerlendirilmesi (Erzincan, Türkiye)</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -524,9 +524,7 @@
       <right style="thin">
         <color rgb="FF999999"/>
       </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -534,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -554,41 +552,17 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -620,9 +594,6 @@
     <xf numFmtId="0" fontId="6" fillId="15" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -665,8 +636,41 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1035,25 +1039,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="56.453125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="104" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="40.81640625" customWidth="1" min="3" max="3"/>
+    <col width="56.6328125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="99.26953125" customWidth="1" min="2" max="2"/>
+    <col width="17.08984375" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="10.81640625" customWidth="1" min="10" max="10"/>
     <col width="48.36328125" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>"Erzincan Jeolojik ve Kültürel Miras" Çalıştayı</t>
         </is>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>📅  18 Haziran (Perşembe) 2026</t>
         </is>
@@ -1065,14 +1069,14 @@
       <c r="C3" s="1" t="n"/>
     </row>
     <row r="4" ht="15.5" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>OTURUM 1 — ERZİNCAN-OTLUKBELİ OTURUMU</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24.5" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
@@ -1106,35 +1110,36 @@
           <t>UNESCO Jeoparkları; Barış Çağrılarından Doğa Korumaya Geçiş</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Nizamettin KAZANCI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>10:00 - 10:30</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Travertine and Calcareous Tufa: “Master Keys” in Geological and Cultural Heritage</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Enrico CAPEZZUOLI</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>10:30 - 10:45  ☕ Çay / Kahve Arası</t>
         </is>
       </c>
+      <c r="C9" s="38" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1147,24 +1152,24 @@
           <t>Otlukbeli Travertenlerinin Jeolojik-Kültürel Mirası ve Erzincan-Otlukbeli Jeopark Potansiyeli</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Yakup ÇELİK / Ezher TAGLIASACCHI / Pınar POLAT / Mehmet Akif TAŞ</t>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yakup ÇELİK </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>11:00 - 11:15</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Jeolojik Miras Envanter Çalışması Aşamaları</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Yıldırım GÜNGÖR</t>
         </is>
@@ -1181,14 +1186,14 @@
           <t>Jeoçeşitlilik ve Çevresel Tehditler</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Raif KANDEMİR</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>12:30 - 13:30  🍽️ Öğle Yemeği</t>
         </is>
@@ -1200,114 +1205,117 @@
       <c r="C14" s="1" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>OTURUM 2 — ERZİNCAN-ÇAĞLAYAN OTURUMU</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>SAAT</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>BİLDİRİ BAŞLIĞI</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>SUNUM YAPAN</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>13:30 - 14:00</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>13:30 - 13:45</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Akarsu Sistemlerinin Doğal Arşivi: Gürlevik Şelalesi ve Jeomiras Potansiyeli</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>Ezher TAGLIASACCHI / Yakup ÇELİK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Ezher TAGLIASACCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="27.5" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>13:45 - 14:00</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Erzincan'ın Jeolojik Miras Alanlarına İlişkin Yeni Örnekler</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ali ERGEN </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>14:00 - 14:15</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
-        <is>
-          <t>Erzincan'ın Jeolojik Miras Alanlarına İlişkin Yeni Örnekler</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Ali ERGEN / Alper BOZKURT / Ayhan ILGAR / Ercan TUNCAY / Tolga ESİRTGEN / Emine ÖZKAN / Mehmet Akif TAŞ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>14:15 - 14:30</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Polat Gölü'nün Jeolojik-Jeomorfolojik Önemi ve Jeomiras Potansiyeli</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
-        <is>
-          <t>Mehmet Akif TAŞ / Pınar POLAT / Yakup ÇELİK / Ezher TAGLIASACCHI</t>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Mehmet Akif TAŞ</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="inlineStr">
-        <is>
-          <t>15:15 - 15:30  ☕ Çay / Kahve Arası</t>
-        </is>
-      </c>
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>14:15 - 14:30  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+      <c r="C21" s="38" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="n"/>
-      <c r="C22" s="1" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="C22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>OTURUM 3 — ERZİNCAN-KEMALİYE OTURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="C23" s="38" t="n"/>
+    </row>
+    <row r="24" ht="8" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="8" customHeight="1">
+      <c r="C24" s="38" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>SAAT</t>
@@ -1327,7 +1335,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>15:30 - 15:45</t>
+          <t>14:30 - 14:45</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1335,127 +1343,130 @@
           <t>Coğrafya ve Tarih: 1473 Otlukbeli Savaşının Yerinin Tespiti ve Yol Güzergahları</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>Kenan İNAN</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>14:45 - 15:00</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>Eşref ATABEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>15:00 - 15:15</t>
+        </is>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>Jeoradar Işığında Erzincan Kalesi ve Kent Meydanı Civarındaki Yapılar</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vedat GÜNGÖR </t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>15:15 - 15:30</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Erzincan'ın Somut Kültürel Miras Değerleri ve Coğrafi Koşullarla Bağlantısı</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>Fatih ORHAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>15:30 - 15:45  ☕ Çay / Kahve Arası</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="n"/>
+    </row>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Oturum Yürütücüleri:</t>
+        </is>
+      </c>
+      <c r="C33" s="38" t="n"/>
+    </row>
+    <row r="34" ht="15.5" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SAAT</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>BİLDİRİ BAŞLIĞI</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>SUNUM YAPAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>15:45 - 16:00</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Jeolojik ve Morfolojik Faktörlerin Erzincan'ın Kültürel Mirasına Katkısı</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Erdal AKPINAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>16:00 - 16:15</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Vedat GÜNGÖR / Mustafa BAYAM (Erzincan Müze Müd.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="44" t="inlineStr">
-        <is>
-          <t>16:15 - 16:45  ☕ Çay / Kahve Arası</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17.5" customHeight="1">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>Oturum Yürütücüleri:</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="8" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>SAAT</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>BİLDİRİ BAŞLIĞI</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>SUNUM YAPAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15.5" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>16:45 - 17:00</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>Ali DEMİRSOY</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>17:00 - 17:15</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Eşref ATABEY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>17:15 - 17:30</t>
+          <t>16:00 - 16:15</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1463,73 +1474,56 @@
           <t>Kuzey Anadolu Fayı'nın Magmatik İzlerinden Jeolojik Mirasa: Erzincan Volkan Konilerinin Jeokimyasal ve Petrojenetik Değerlendirmesi</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Fatma Şişman TÜKEL / Yakup ÇELİK / Ali ERGEN</t>
+      <c r="C36" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatma Şişman TÜKEL </t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>17:30 - 17:45</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>M. Feridun ÇELİKMEN (KEMAV Başkanı)</t>
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>16:15 - 16:30</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>Konarlı Şelalesi (Tercan)</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>Pınar POLAT</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>17:45 - 18:00</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>Pınar POLAT</t>
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>16:30 - 16:45</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mutlu SEVEN </t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>18:00 - 18:15</t>
-        </is>
-      </c>
-      <c r="B39" s="21" t="inlineStr">
-        <is>
-          <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli Açısından Değerlendirilmesi (Erzincan, Türkiye)</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Mutlu SEVEN / Yahya ÖZTÜRK</t>
-        </is>
-      </c>
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="n"/>
-    </row>
-    <row r="41">
-      <c r="C41" s="30" t="n"/>
+      <c r="C40" s="21" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="1200"/>
 </worksheet>
 </file>
 

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1140" yWindow="1140" windowWidth="32710" windowHeight="18040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1416,7 +1416,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>OTURUM 4 — ERZİNCAN KARMA OTURUM</t>
+          <t>OTURUM 4 — ERZİNCAN ÜZÜMLÜ OTURUM</t>
         </is>
       </c>
       <c r="C32" s="38" t="n"/>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1416,7 +1416,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>OTURUM 4 — ERZİNCAN ÜZÜMLÜ OTURUM</t>
+          <t>OTURUM 4 — ERZİNCAN ÜZÜMLÜ OTURUMU</t>
         </is>
       </c>
       <c r="C32" s="38" t="n"/>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1335,138 +1335,138 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>14:30 - 14:45</t>
+          <t>14:30 - 14:42</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>Ali DEMİRSOY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>14:42 - 14:54</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
           <t>Coğrafya ve Tarih: 1473 Otlukbeli Savaşının Yerinin Tespiti ve Yol Güzergahları</t>
         </is>
       </c>
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>Kenan İNAN</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>14:45 - 15:00</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>14:54 - 15:06</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Kemaliye'nin Jeolojisi, Doğa Değerleri, Antropojenik Tehlikeler ve Koruma Statüsü</t>
         </is>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>Eşref ATABEY</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>15:00 - 15:15</t>
-        </is>
-      </c>
-      <c r="B28" s="46" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>15:06 - 15:18</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Jeoradar Işığında Erzincan Kalesi ve Kent Meydanı Civarındaki Yapılar</t>
         </is>
       </c>
-      <c r="C28" s="39" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Vedat GÜNGÖR </t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>15:15 - 15:30</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>15:18 - 15:30</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Erzincan'ın Somut Kültürel Miras Değerleri ve Coğrafi Koşullarla Bağlantısı</t>
         </is>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>Fatih ORHAN</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="17.5" customHeight="1">
-      <c r="A30" s="45" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t>15:30 - 15:45  ☕ Çay / Kahve Arası</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="42" t="n"/>
+      <c r="C31" s="38" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>OTURUM 4 — ERZİNCAN ÜZÜMLÜ OTURUMU</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n"/>
-    </row>
-    <row r="33" ht="8" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="C33" s="38" t="n"/>
+    </row>
+    <row r="34" ht="15.5" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>Oturum Yürütücüleri:</t>
         </is>
       </c>
-      <c r="C33" s="38" t="n"/>
-    </row>
-    <row r="34" ht="15.5" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="C34" s="38" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>SAAT</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>BİLDİRİ BAŞLIĞI</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>SUNUM YAPAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>15:45 - 16:00</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Erzincan'ın Biyoçeşitliliğinin Tarihsel Gelişimi ve Önemi: Kemaliye Prof. Dr. Ali Demirsoy Doğa Tarihi Müzesi</t>
-        </is>
-      </c>
-      <c r="C35" s="36" t="inlineStr">
-        <is>
-          <t>Ali DEMİRSOY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>16:00 - 16:15</t>
+          <t>15:45 - 16:05</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1481,29 +1481,29 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>16:15 - 16:30</t>
-        </is>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>16:05 - 16:25</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Konarlı Şelalesi (Tercan)</t>
         </is>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>Pınar POLAT</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>16:30 - 16:45</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>16:25 - 16:45</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Esence (Keşiş) Dağları'nda Buzul Jeomorfolojisinin Jeomiras Potansiyeli</t>
         </is>

--- a/fotolar/sunum-taslak.xlsx
+++ b/fotolar/sunum-taslak.xlsx
@@ -1238,7 +1238,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>13:30 - 13:45</t>
+          <t>13:30 - 14:00</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="19" ht="27.5" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>13:45 - 14:00</t>
+          <t>14:00 - 14:30</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>14:00 - 14:15</t>
+          <t>14:30 - 14:45</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>14:15 - 14:30  ☕ Çay / Kahve Arası</t>
+          <t>14:45 - 15:00  ☕ Çay / Kahve Arası</t>
         </is>
       </c>
       <c r="C21" s="38" t="n"/>
@@ -1335,7 +1335,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>14:30 - 14:42</t>
+          <t>15:00 - 15:30</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1352,7 +1352,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>14:42 - 14:54</t>
+          <t>15:30 - 16:00</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>14:54 - 15:06</t>
+          <t>16:00 - 16:15</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1386,7 +1386,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>15:06 - 15:18</t>
+          <t>16:15 - 16:30</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="30" ht="17.5" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>15:18 - 15:30</t>
+          <t>16:30 - 16:45</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
     <row r="31">
       <c r="A31" s="45" t="inlineStr">
         <is>
-          <t>15:30 - 15:45  ☕ Çay / Kahve Arası</t>
+          <t>16:45 - 17:00  ☕ Çay / Kahve Arası</t>
         </is>
       </c>
       <c r="C31" s="38" t="n"/>
@@ -1466,7 +1466,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>15:45 - 16:05</t>
+          <t>17:00 - 17:30</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>16:05 - 16:25</t>
+          <t>17:30 - 18:00</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>16:25 - 16:45</t>
+          <t>18:00 - 18:15</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
